--- a/DateBase/orders/Nha Thu_2026-5-7.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-7.xlsx
@@ -1356,6 +1356,9 @@
       <c r="G2" t="str">
         <v>0151555520203020101457552553631522510410101510155331020555105101051010535555305101010201510515101610105101961011105105101015105515301020101010205201551055301015</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
